--- a/job_scrape_11_05_13_36.xlsx
+++ b/job_scrape_11_05_13_36.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\linkedin_automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3881408-4CA4-45ED-9479-84E6A975D1E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FBD1347-F623-4CF6-8BEC-F8A8A88AFAD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$51</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="159">
   <si>
     <t>company</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>german_skills</t>
+  </si>
+  <si>
+    <t>german_needed</t>
   </si>
   <si>
     <t>Anker Innovations</t>
@@ -1508,18 +1511,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1542,19 +1537,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1855,14 +1844,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="53.5703125" style="1" customWidth="1"/>
+    <col min="1" max="3" width="22.28515625" customWidth="1"/>
+    <col min="4" max="4" width="36.42578125" customWidth="1"/>
+    <col min="5" max="5" width="22.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1872,683 +1862,823 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="90" x14ac:dyDescent="0.25">
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="135" x14ac:dyDescent="0.25">
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4"/>
-    </row>
-    <row r="5" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="E4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>20</v>
       </c>
-      <c r="C6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="B9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" t="s">
         <v>22</v>
       </c>
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="E9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" ht="90" x14ac:dyDescent="0.25">
+      <c r="D10" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11" s="1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D11" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+      <c r="E12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" t="s">
+        <v>43</v>
+      </c>
+      <c r="E13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" t="s">
+        <v>47</v>
+      </c>
+      <c r="E14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" t="s">
+        <v>55</v>
+      </c>
+      <c r="E16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>56</v>
+      </c>
+      <c r="B17" t="s">
+        <v>57</v>
+      </c>
+      <c r="C17" t="s">
+        <v>58</v>
+      </c>
+      <c r="D17" t="s">
+        <v>59</v>
+      </c>
+      <c r="E17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>60</v>
+      </c>
+      <c r="B18" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18" t="s">
+        <v>62</v>
+      </c>
+      <c r="D18" t="s">
+        <v>63</v>
+      </c>
+      <c r="E18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>64</v>
+      </c>
+      <c r="B19" t="s">
+        <v>65</v>
+      </c>
+      <c r="C19" t="s">
+        <v>66</v>
+      </c>
+      <c r="D19" t="s">
+        <v>67</v>
+      </c>
+      <c r="E19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>68</v>
+      </c>
+      <c r="B20" t="s">
+        <v>69</v>
+      </c>
+      <c r="C20" t="s">
+        <v>70</v>
+      </c>
+      <c r="D20" t="s">
+        <v>71</v>
+      </c>
+      <c r="E20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>72</v>
+      </c>
+      <c r="B21" t="s">
+        <v>73</v>
+      </c>
+      <c r="C21" t="s">
+        <v>74</v>
+      </c>
+      <c r="D21" t="s">
+        <v>75</v>
+      </c>
+      <c r="E21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>76</v>
+      </c>
+      <c r="B22" t="s">
+        <v>77</v>
+      </c>
+      <c r="C22" t="s">
+        <v>78</v>
+      </c>
+      <c r="D22" t="s">
+        <v>79</v>
+      </c>
+      <c r="E22" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>41</v>
       </c>
-      <c r="C13" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="180" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" t="s">
-        <v>44</v>
-      </c>
-      <c r="C14" t="s">
-        <v>45</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="120" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>47</v>
-      </c>
-      <c r="B15" t="s">
-        <v>48</v>
-      </c>
-      <c r="C15" t="s">
-        <v>49</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="285" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>51</v>
-      </c>
-      <c r="B16" t="s">
-        <v>52</v>
-      </c>
-      <c r="C16" t="s">
-        <v>53</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="90" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>55</v>
-      </c>
-      <c r="B17" t="s">
-        <v>56</v>
-      </c>
-      <c r="C17" t="s">
-        <v>57</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="105" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>59</v>
-      </c>
-      <c r="B18" t="s">
-        <v>60</v>
-      </c>
-      <c r="C18" t="s">
-        <v>61</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="285" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>63</v>
-      </c>
-      <c r="B19" t="s">
-        <v>64</v>
-      </c>
-      <c r="C19" t="s">
-        <v>65</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>67</v>
-      </c>
-      <c r="B20" t="s">
-        <v>68</v>
-      </c>
-      <c r="C20" t="s">
-        <v>69</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>71</v>
-      </c>
-      <c r="B21" t="s">
+      <c r="B23" t="s">
+        <v>80</v>
+      </c>
+      <c r="C23" t="s">
+        <v>81</v>
+      </c>
+      <c r="D23" t="s">
+        <v>82</v>
+      </c>
+      <c r="E23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>83</v>
+      </c>
+      <c r="B24" t="s">
+        <v>84</v>
+      </c>
+      <c r="C24" t="s">
+        <v>85</v>
+      </c>
+      <c r="D24" t="s">
+        <v>86</v>
+      </c>
+      <c r="E24" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>87</v>
+      </c>
+      <c r="B25" t="s">
+        <v>88</v>
+      </c>
+      <c r="C25" t="s">
+        <v>89</v>
+      </c>
+      <c r="D25" t="s">
+        <v>90</v>
+      </c>
+      <c r="E25" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>76</v>
+      </c>
+      <c r="B26" t="s">
+        <v>91</v>
+      </c>
+      <c r="C26" t="s">
+        <v>92</v>
+      </c>
+      <c r="D26" t="s">
+        <v>93</v>
+      </c>
+      <c r="E26" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>94</v>
+      </c>
+      <c r="B27" t="s">
+        <v>95</v>
+      </c>
+      <c r="C27" t="s">
+        <v>96</v>
+      </c>
+      <c r="D27" t="s">
+        <v>97</v>
+      </c>
+      <c r="E27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>98</v>
+      </c>
+      <c r="B28" t="s">
+        <v>99</v>
+      </c>
+      <c r="C28" t="s">
+        <v>100</v>
+      </c>
+      <c r="D28" t="s">
+        <v>101</v>
+      </c>
+      <c r="E28" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>102</v>
+      </c>
+      <c r="B29" t="s">
+        <v>103</v>
+      </c>
+      <c r="C29" t="s">
+        <v>104</v>
+      </c>
+      <c r="D29" t="s">
+        <v>105</v>
+      </c>
+      <c r="E29" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>102</v>
+      </c>
+      <c r="B30" t="s">
+        <v>106</v>
+      </c>
+      <c r="C30" t="s">
+        <v>104</v>
+      </c>
+      <c r="D30" t="s">
+        <v>105</v>
+      </c>
+      <c r="E30" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>72</v>
       </c>
-      <c r="C21" t="s">
-        <v>73</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>75</v>
-      </c>
-      <c r="B22" t="s">
+      <c r="B31" t="s">
+        <v>107</v>
+      </c>
+      <c r="C31" t="s">
+        <v>108</v>
+      </c>
+      <c r="D31" t="s">
+        <v>109</v>
+      </c>
+      <c r="E31" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" t="s">
+        <v>110</v>
+      </c>
+      <c r="C32" t="s">
+        <v>111</v>
+      </c>
+      <c r="E32" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>41</v>
+      </c>
+      <c r="B33" t="s">
+        <v>112</v>
+      </c>
+      <c r="C33" t="s">
+        <v>113</v>
+      </c>
+      <c r="D33" t="s">
+        <v>114</v>
+      </c>
+      <c r="E33" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>115</v>
+      </c>
+      <c r="B34" t="s">
+        <v>116</v>
+      </c>
+      <c r="C34" t="s">
+        <v>117</v>
+      </c>
+      <c r="D34" t="s">
+        <v>118</v>
+      </c>
+      <c r="E34" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>119</v>
+      </c>
+      <c r="B35" t="s">
+        <v>120</v>
+      </c>
+      <c r="C35" t="s">
+        <v>121</v>
+      </c>
+      <c r="D35" t="s">
+        <v>122</v>
+      </c>
+      <c r="E35" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>76</v>
       </c>
-      <c r="C22" t="s">
-        <v>77</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>40</v>
-      </c>
-      <c r="B23" t="s">
-        <v>79</v>
-      </c>
-      <c r="C23" t="s">
-        <v>80</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>82</v>
-      </c>
-      <c r="B24" t="s">
-        <v>83</v>
-      </c>
-      <c r="C24" t="s">
-        <v>84</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="75" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>86</v>
-      </c>
-      <c r="B25" t="s">
-        <v>87</v>
-      </c>
-      <c r="C25" t="s">
-        <v>88</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>75</v>
-      </c>
-      <c r="B26" t="s">
-        <v>90</v>
-      </c>
-      <c r="C26" t="s">
-        <v>91</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="75" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>93</v>
-      </c>
-      <c r="B27" t="s">
-        <v>94</v>
-      </c>
-      <c r="C27" t="s">
-        <v>95</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>97</v>
-      </c>
-      <c r="B28" t="s">
-        <v>98</v>
-      </c>
-      <c r="C28" t="s">
-        <v>99</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="90" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>101</v>
-      </c>
-      <c r="B29" t="s">
-        <v>102</v>
-      </c>
-      <c r="C29" t="s">
-        <v>103</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="90" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B30" t="s">
-        <v>105</v>
-      </c>
-      <c r="C30" t="s">
-        <v>103</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>71</v>
-      </c>
-      <c r="B31" t="s">
-        <v>106</v>
-      </c>
-      <c r="C31" t="s">
-        <v>107</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>40</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>40</v>
-      </c>
-      <c r="B33" t="s">
-        <v>111</v>
-      </c>
-      <c r="C33" t="s">
-        <v>112</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+      <c r="B36" t="s">
+        <v>123</v>
+      </c>
+      <c r="C36" t="s">
+        <v>124</v>
+      </c>
+      <c r="E36" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>125</v>
+      </c>
+      <c r="B37" t="s">
+        <v>126</v>
+      </c>
+      <c r="C37" t="s">
+        <v>127</v>
+      </c>
+      <c r="E37" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>125</v>
+      </c>
+      <c r="B38" t="s">
+        <v>126</v>
+      </c>
+      <c r="C38" t="s">
+        <v>127</v>
+      </c>
+      <c r="E38" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>76</v>
+      </c>
+      <c r="B39" t="s">
+        <v>128</v>
+      </c>
+      <c r="C39" t="s">
+        <v>129</v>
+      </c>
+      <c r="D39" t="s">
+        <v>130</v>
+      </c>
+      <c r="E39" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>131</v>
+      </c>
+      <c r="B40" t="s">
+        <v>132</v>
+      </c>
+      <c r="C40" t="s">
+        <v>133</v>
+      </c>
+      <c r="E40" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>134</v>
+      </c>
+      <c r="B41" t="s">
+        <v>135</v>
+      </c>
+      <c r="C41" t="s">
+        <v>136</v>
+      </c>
+      <c r="E41" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>137</v>
+      </c>
+      <c r="C42" t="s">
+        <v>138</v>
+      </c>
+      <c r="D42" t="s">
         <v>114</v>
       </c>
-      <c r="B34" t="s">
-        <v>115</v>
-      </c>
-      <c r="C34" t="s">
-        <v>116</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" ht="90" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>118</v>
-      </c>
-      <c r="B35" t="s">
-        <v>119</v>
-      </c>
-      <c r="C35" t="s">
-        <v>120</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>75</v>
-      </c>
-      <c r="B36" t="s">
-        <v>122</v>
-      </c>
-      <c r="C36" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>124</v>
-      </c>
-      <c r="B37" s="2" t="s">
+      <c r="E42" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>41</v>
+      </c>
+      <c r="B43" t="s">
+        <v>139</v>
+      </c>
+      <c r="C43" t="s">
+        <v>140</v>
+      </c>
+      <c r="D43" t="s">
+        <v>114</v>
+      </c>
+      <c r="E43" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>141</v>
+      </c>
+      <c r="B44" t="s">
+        <v>142</v>
+      </c>
+      <c r="C44" t="s">
+        <v>143</v>
+      </c>
+      <c r="D44" t="s">
+        <v>144</v>
+      </c>
+      <c r="E44" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>141</v>
+      </c>
+      <c r="B45" t="s">
+        <v>142</v>
+      </c>
+      <c r="C45" t="s">
+        <v>143</v>
+      </c>
+      <c r="D45" t="s">
+        <v>144</v>
+      </c>
+      <c r="E45" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>41</v>
+      </c>
+      <c r="B46" t="s">
+        <v>145</v>
+      </c>
+      <c r="C46" t="s">
+        <v>146</v>
+      </c>
+      <c r="D46" t="s">
+        <v>114</v>
+      </c>
+      <c r="E46" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>41</v>
+      </c>
+      <c r="B47" t="s">
+        <v>145</v>
+      </c>
+      <c r="C47" t="s">
+        <v>146</v>
+      </c>
+      <c r="D47" t="s">
+        <v>114</v>
+      </c>
+      <c r="E47" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>147</v>
+      </c>
+      <c r="B48" t="s">
+        <v>148</v>
+      </c>
+      <c r="C48" t="s">
+        <v>149</v>
+      </c>
+      <c r="D48" t="s">
+        <v>150</v>
+      </c>
+      <c r="E48" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
         <v>125</v>
       </c>
-      <c r="C37" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>124</v>
-      </c>
-      <c r="B38" t="s">
-        <v>125</v>
-      </c>
-      <c r="C38" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" ht="120" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>75</v>
-      </c>
-      <c r="B39" t="s">
-        <v>127</v>
-      </c>
-      <c r="C39" t="s">
-        <v>128</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>130</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C40" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>133</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="C41" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42" t="s">
-        <v>136</v>
-      </c>
-      <c r="C42" t="s">
-        <v>137</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>40</v>
-      </c>
-      <c r="B43" t="s">
-        <v>138</v>
-      </c>
-      <c r="C43" t="s">
-        <v>139</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>140</v>
-      </c>
-      <c r="B44" t="s">
-        <v>141</v>
-      </c>
-      <c r="C44" t="s">
-        <v>142</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>140</v>
-      </c>
-      <c r="B45" t="s">
-        <v>141</v>
-      </c>
-      <c r="C45" t="s">
-        <v>142</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" t="s">
-        <v>144</v>
-      </c>
-      <c r="C46" t="s">
-        <v>145</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" t="s">
-        <v>144</v>
-      </c>
-      <c r="C47" t="s">
-        <v>145</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" ht="90" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>146</v>
-      </c>
-      <c r="B48" t="s">
-        <v>147</v>
-      </c>
-      <c r="C48" t="s">
-        <v>148</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>124</v>
-      </c>
       <c r="B49" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C49" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+      <c r="E49" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B50" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C50" t="s">
-        <v>153</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+      <c r="D50" t="s">
+        <v>114</v>
+      </c>
+      <c r="E50" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B51" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C51" t="s">
-        <v>156</v>
-      </c>
-      <c r="D51" s="1" t="s">
         <v>157</v>
       </c>
+      <c r="D51" t="s">
+        <v>158</v>
+      </c>
+      <c r="E51" t="b">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D51" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="3">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-  </autoFilter>
-  <hyperlinks>
-    <hyperlink ref="B32" r:id="rId1" xr:uid="{C3C12479-BCF4-4AA4-86A7-5DD77ACD7E93}"/>
-    <hyperlink ref="B37" r:id="rId2" xr:uid="{08A61482-904A-4FBB-8E32-1EE8EEBB0A37}"/>
-    <hyperlink ref="B40" r:id="rId3" xr:uid="{73836EEE-6670-43B0-8D97-54DD88BF280C}"/>
-    <hyperlink ref="B41" r:id="rId4" xr:uid="{AFDD271A-C09D-4365-B0D6-4CA503C75452}"/>
-  </hyperlinks>
+  <autoFilter ref="A1:E51" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>